--- a/Lab_8/ЛР№8_Проєкт_Маркетингова_стратегія_2025.xlsx
+++ b/Lab_8/ЛР№8_Проєкт_Маркетингова_стратегія_2025.xlsx
@@ -8,20 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ІФТКН\3 КУРС\1 семестр\Маркетинг IT-продуктів\Marketing\Lab_8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9157DC16-28BE-4D67-BD95-257C987AF5EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8820B7B2-2662-4E06-93B6-B62D9B07FB6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="311" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="14.Affiliate marketing" sheetId="9" r:id="rId1"/>
-    <sheet name="Аркуш1" sheetId="10" r:id="rId2"/>
   </sheets>
   <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
   <si>
     <t>Категорія</t>
   </si>
@@ -131,15 +130,6 @@
     <t>Отримати 200 завантажень/реєстрацій через тизер-відео з кліпами новинок.</t>
   </si>
   <si>
-    <t>Анімований банер з постером фільму та CTA</t>
-  </si>
-  <si>
-    <t>Карусель з постерами та короткими описами</t>
-  </si>
-  <si>
-    <t>Тизер-відео з кліпом трейлера</t>
-  </si>
-  <si>
     <t>300x250 px</t>
   </si>
   <si>
@@ -149,29 +139,14 @@
     <t>320x50 px</t>
   </si>
   <si>
-    <t>Використовувати кольори: синій для довіри, червоний для енергії. A/B тестування з/без анімації.</t>
-  </si>
-  <si>
-    <t>Додати хештеги #CineCloud #MovieNight. Таргетинг на 18-35 років, інтереси: кіно.</t>
-  </si>
-  <si>
-    <t>Оптимізувати для мобільних, вага &lt;150 KB. Комісія для affiliates: 20% від першої підписки.</t>
-  </si>
-  <si>
-    <t>Згідно з Google Ads стандартами</t>
-  </si>
-  <si>
-    <t>Згідно з Instagram specs</t>
-  </si>
-  <si>
-    <t>Згідно з мобільними IAB стандартами</t>
+    <t>Статичний банер</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -208,13 +183,6 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="204"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -278,9 +246,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -313,19 +281,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -573,10 +532,10 @@
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="12" t="s">
         <v>23</v>
       </c>
       <c r="D2" s="11" t="s">
@@ -587,13 +546,13 @@
       <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="13" t="s">
         <v>26</v>
       </c>
     </row>
@@ -601,13 +560,13 @@
       <c r="A4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="13" t="s">
         <v>29</v>
       </c>
     </row>
@@ -615,13 +574,13 @@
       <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="13" t="s">
         <v>32</v>
       </c>
     </row>
@@ -629,13 +588,13 @@
       <c r="A6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="13" t="s">
         <v>35</v>
       </c>
     </row>
@@ -643,13 +602,13 @@
       <c r="A7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="13" t="s">
         <v>16</v>
       </c>
     </row>
@@ -657,13 +616,13 @@
       <c r="A8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="13" t="s">
         <v>19</v>
       </c>
     </row>
@@ -671,28 +630,28 @@
       <c r="A9" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>38</v>
+      <c r="B9" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>41</v>
+      <c r="B10" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -719,198 +678,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07FCF5F2-4BCE-492E-98CF-A8D0001F83D8}">
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:4" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="316.8" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="145.19999999999999" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="224.4" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="92.4" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="79.2" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-    </row>
-    <row r="13" spans="1:4" ht="171.6" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="145.19999999999999" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>47</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{31FCFBC5-BCD8-4A0F-AEAD-27D0607848DD}"/>
-    <hyperlink ref="C2" r:id="rId2" xr:uid="{61473030-4395-4CBB-B483-AD8869AD16A8}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>